--- a/Config/GameConfig/Datas/errorcode.xlsx
+++ b/Config/GameConfig/Datas/errorcode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56B3532-9B05-4EEF-BA30-239641AD9536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47E20B2-C6C9-4E3B-A43D-C6B08B0A713F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -163,12 +163,146 @@
   <si>
     <t>G2C_BuildCenterRoute_Resp</t>
   </si>
+  <si>
+    <t>C2Center_SetNickName_Req</t>
+  </si>
+  <si>
+    <t>Center2C_SetNickName_Resp</t>
+  </si>
+  <si>
+    <t>请求修改昵称</t>
+  </si>
+  <si>
+    <t>C2Center_GetPlayerData_Req</t>
+  </si>
+  <si>
+    <t>Center2C_GetPlayerData_Resp</t>
+  </si>
+  <si>
+    <t>请求获取玩家数据</t>
+  </si>
+  <si>
+    <t>C2Center_Farmland_GetFarmlandData_Req</t>
+  </si>
+  <si>
+    <t>通用模块</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>农田模块</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center2C_Farmland_GetFarmlandData_Resp</t>
+  </si>
+  <si>
+    <t>请求农田信息</t>
+  </si>
+  <si>
+    <t>数据不存在</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>请求农田被偷信息</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2Center_Farmland_GetStealInfo_Req</t>
+  </si>
+  <si>
+    <t>Center2C_Farmland_GetStealInfo_Resp</t>
+  </si>
+  <si>
+    <t>请求解锁农田</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2Center_Farmland_UnlockLand_Req</t>
+  </si>
+  <si>
+    <t>Center2C_Farmland_UnlockLand_Resp</t>
+  </si>
+  <si>
+    <t>请求修改农田类型</t>
+  </si>
+  <si>
+    <t>C2Center_Farmland_ChangeLandType_Req</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center2C_Farmland_ChangeLandType_Resp</t>
+  </si>
+  <si>
+    <t>请求种植</t>
+  </si>
+  <si>
+    <t>C2Center_Farmland_Seed_Req</t>
+  </si>
+  <si>
+    <t>Center2C_Farmland_Seed_Resp</t>
+  </si>
+  <si>
+    <t>请求收获</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2Center_Farmland_GainYield_Req</t>
+  </si>
+  <si>
+    <t>Center2C_Farmland_GainYield_Resp</t>
+  </si>
+  <si>
+    <t>请求铲除作物</t>
+  </si>
+  <si>
+    <t>C2Center_Farmland_RemoveCrop_Req</t>
+  </si>
+  <si>
+    <t>Center2C_Farmland_RemoveCrop_Resp</t>
+  </si>
+  <si>
+    <t>请求偷菜</t>
+  </si>
+  <si>
+    <t>C2Center_Farmland_StealYield_Req</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center2C_Farmland_StealYield_Resp</t>
+  </si>
+  <si>
+    <t>请求浇水</t>
+  </si>
+  <si>
+    <t>C2Center_Farmland_Water_Req</t>
+  </si>
+  <si>
+    <t>Center2C_Farmland_Water_Resp</t>
+  </si>
+  <si>
+    <t>请求施肥</t>
+  </si>
+  <si>
+    <t>C2Center_Farmland_Fertilizer_Req</t>
+  </si>
+  <si>
+    <t>Center2C_Farmland_Fertilizer_Resp</t>
+  </si>
+  <si>
+    <t>请求除虫</t>
+  </si>
+  <si>
+    <t>C2Center_Farmland_DePest_Req</t>
+  </si>
+  <si>
+    <t>Center2C_Farmland_DePest_Resp</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +345,25 @@
       <sz val="11"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6A9955"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -275,7 +428,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
@@ -284,6 +437,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="2" builtinId="27"/>
@@ -566,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" customWidth="1"/>
@@ -697,24 +858,231 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="B6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="B7">
         <v>10001</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>13</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G7" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>10002</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>10003</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>20001</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>20002</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>20003</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>20004</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>20005</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>20006</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>20007</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>20008</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>20009</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>20010</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>20011</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
